--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dines\Downloads\python project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF6596C7-7601-44D1-B9DE-34E4550A1C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B1FD29-3DD4-4935-A218-E80004A0E14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8964" xr2:uid="{BB727521-3A36-4C26-86D4-87332573593B}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="49">
   <si>
     <t>name</t>
   </si>
@@ -1007,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{611DFE69-D96B-4198-A2DF-4C75AC3C3711}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1667,7 +1667,7 @@
         <v>90</v>
       </c>
       <c r="D39">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="E39">
         <v>50</v>
@@ -1675,36 +1675,36 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
       </c>
       <c r="C40">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D40">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E40">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
         <v>6</v>
       </c>
       <c r="C41">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D41">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E41">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1715,29 +1715,46 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D42">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="E42">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43">
+        <v>110</v>
+      </c>
+      <c r="D43">
+        <v>135</v>
+      </c>
+      <c r="E43">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>48</v>
       </c>
-      <c r="B43" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43">
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44">
         <v>130</v>
       </c>
-      <c r="D43">
+      <c r="D44">
         <v>155</v>
       </c>
-      <c r="E43">
+      <c r="E44">
         <v>20</v>
       </c>
     </row>
